--- a/artfynd/A 31821-2021 artfynd.xlsx
+++ b/artfynd/A 31821-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122651416</v>
+        <v>122651412</v>
       </c>
       <c r="B2" t="n">
-        <v>90798</v>
+        <v>90853</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5447</v>
+        <v>5442</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>556434</v>
+        <v>556358</v>
       </c>
       <c r="R2" t="n">
-        <v>6510117</v>
+        <v>6510128</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122651415</v>
+        <v>122651416</v>
       </c>
       <c r="B3" t="n">
-        <v>95011</v>
+        <v>90798</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,21 +803,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2180</v>
+        <v>5447</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>556376</v>
+        <v>556434</v>
       </c>
       <c r="R3" t="n">
-        <v>6510108</v>
+        <v>6510117</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122651412</v>
+        <v>122651415</v>
       </c>
       <c r="B4" t="n">
-        <v>90853</v>
+        <v>95011</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -911,25 +911,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5442</v>
+        <v>2180</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -939,10 +939,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>556358</v>
+        <v>556376</v>
       </c>
       <c r="R4" t="n">
-        <v>6510128</v>
+        <v>6510108</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -974,7 +974,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 31821-2021 artfynd.xlsx
+++ b/artfynd/A 31821-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122651412</v>
       </c>
       <c r="B2" t="n">
-        <v>90853</v>
+        <v>90854</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122651416</v>
+        <v>122651415</v>
       </c>
       <c r="B3" t="n">
-        <v>90798</v>
+        <v>95012</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,21 +803,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5447</v>
+        <v>2180</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>556434</v>
+        <v>556376</v>
       </c>
       <c r="R3" t="n">
-        <v>6510117</v>
+        <v>6510108</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122651415</v>
+        <v>122651411</v>
       </c>
       <c r="B4" t="n">
-        <v>95011</v>
+        <v>78302</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -911,25 +911,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2180</v>
+        <v>353</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -939,10 +939,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>556376</v>
+        <v>556360</v>
       </c>
       <c r="R4" t="n">
-        <v>6510108</v>
+        <v>6510120</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -974,7 +974,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122651411</v>
+        <v>122651416</v>
       </c>
       <c r="B5" t="n">
-        <v>78301</v>
+        <v>90799</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1023,25 +1023,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>353</v>
+        <v>5447</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1051,10 +1051,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>556360</v>
+        <v>556434</v>
       </c>
       <c r="R5" t="n">
-        <v>6510120</v>
+        <v>6510117</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1086,7 +1086,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 31821-2021 artfynd.xlsx
+++ b/artfynd/A 31821-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122651412</v>
+        <v>122651415</v>
       </c>
       <c r="B2" t="n">
-        <v>90854</v>
+        <v>95015</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5442</v>
+        <v>2180</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>556358</v>
+        <v>556376</v>
       </c>
       <c r="R2" t="n">
-        <v>6510128</v>
+        <v>6510108</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122651415</v>
+        <v>122651411</v>
       </c>
       <c r="B3" t="n">
-        <v>95012</v>
+        <v>78305</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -799,25 +799,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2180</v>
+        <v>353</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>556376</v>
+        <v>556360</v>
       </c>
       <c r="R3" t="n">
-        <v>6510108</v>
+        <v>6510120</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122651411</v>
+        <v>122651416</v>
       </c>
       <c r="B4" t="n">
-        <v>78302</v>
+        <v>90802</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -911,25 +911,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>353</v>
+        <v>5447</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -939,10 +939,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>556360</v>
+        <v>556434</v>
       </c>
       <c r="R4" t="n">
-        <v>6510120</v>
+        <v>6510117</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -974,7 +974,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122651416</v>
+        <v>122651412</v>
       </c>
       <c r="B5" t="n">
-        <v>90799</v>
+        <v>90857</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1023,25 +1023,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5447</v>
+        <v>5442</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1051,10 +1051,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>556434</v>
+        <v>556358</v>
       </c>
       <c r="R5" t="n">
-        <v>6510117</v>
+        <v>6510128</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1086,7 +1086,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 31821-2021 artfynd.xlsx
+++ b/artfynd/A 31821-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122651415</v>
+        <v>122651416</v>
       </c>
       <c r="B2" t="n">
-        <v>95015</v>
+        <v>90802</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2180</v>
+        <v>5447</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>556376</v>
+        <v>556434</v>
       </c>
       <c r="R2" t="n">
-        <v>6510108</v>
+        <v>6510117</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122651411</v>
+        <v>122651412</v>
       </c>
       <c r="B3" t="n">
-        <v>78305</v>
+        <v>90857</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,21 +803,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>353</v>
+        <v>5442</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>556360</v>
+        <v>556358</v>
       </c>
       <c r="R3" t="n">
-        <v>6510120</v>
+        <v>6510128</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122651416</v>
+        <v>122651415</v>
       </c>
       <c r="B4" t="n">
-        <v>90802</v>
+        <v>95015</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,21 +915,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5447</v>
+        <v>2180</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -939,10 +939,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>556434</v>
+        <v>556376</v>
       </c>
       <c r="R4" t="n">
-        <v>6510117</v>
+        <v>6510108</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -974,7 +974,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122651412</v>
+        <v>122651411</v>
       </c>
       <c r="B5" t="n">
-        <v>90857</v>
+        <v>78305</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1027,21 +1027,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5442</v>
+        <v>353</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1051,10 +1051,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>556358</v>
+        <v>556360</v>
       </c>
       <c r="R5" t="n">
-        <v>6510128</v>
+        <v>6510120</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1086,7 +1086,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 31821-2021 artfynd.xlsx
+++ b/artfynd/A 31821-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122651416</v>
+        <v>122651415</v>
       </c>
       <c r="B2" t="n">
-        <v>90802</v>
+        <v>95118</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5447</v>
+        <v>2180</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>556434</v>
+        <v>556376</v>
       </c>
       <c r="R2" t="n">
-        <v>6510117</v>
+        <v>6510108</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -790,7 +790,7 @@
         <v>122651412</v>
       </c>
       <c r="B3" t="n">
-        <v>90857</v>
+        <v>90960</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -899,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122651415</v>
+        <v>122651416</v>
       </c>
       <c r="B4" t="n">
-        <v>95015</v>
+        <v>90905</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,21 +915,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2180</v>
+        <v>5447</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -939,10 +939,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>556376</v>
+        <v>556434</v>
       </c>
       <c r="R4" t="n">
-        <v>6510108</v>
+        <v>6510117</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -974,7 +974,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1014,7 +1014,7 @@
         <v>122651411</v>
       </c>
       <c r="B5" t="n">
-        <v>78305</v>
+        <v>78407</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>

--- a/artfynd/A 31821-2021 artfynd.xlsx
+++ b/artfynd/A 31821-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122651415</v>
+        <v>122651412</v>
       </c>
       <c r="B2" t="n">
-        <v>95118</v>
+        <v>90960</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2180</v>
+        <v>5442</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>556376</v>
+        <v>556358</v>
       </c>
       <c r="R2" t="n">
-        <v>6510108</v>
+        <v>6510128</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122651412</v>
+        <v>122651415</v>
       </c>
       <c r="B3" t="n">
-        <v>90960</v>
+        <v>95118</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -799,25 +799,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5442</v>
+        <v>2180</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>556358</v>
+        <v>556376</v>
       </c>
       <c r="R3" t="n">
-        <v>6510128</v>
+        <v>6510108</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 31821-2021 artfynd.xlsx
+++ b/artfynd/A 31821-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122651412</v>
+        <v>122651416</v>
       </c>
       <c r="B2" t="n">
-        <v>90960</v>
+        <v>90909</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5442</v>
+        <v>5447</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>556358</v>
+        <v>556434</v>
       </c>
       <c r="R2" t="n">
-        <v>6510128</v>
+        <v>6510117</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -790,7 +790,7 @@
         <v>122651415</v>
       </c>
       <c r="B3" t="n">
-        <v>95118</v>
+        <v>95126</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -899,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122651416</v>
+        <v>122651411</v>
       </c>
       <c r="B4" t="n">
-        <v>90905</v>
+        <v>78411</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -911,25 +911,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5447</v>
+        <v>353</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -939,10 +939,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>556434</v>
+        <v>556360</v>
       </c>
       <c r="R4" t="n">
-        <v>6510117</v>
+        <v>6510120</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -974,7 +974,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122651411</v>
+        <v>122651412</v>
       </c>
       <c r="B5" t="n">
-        <v>78407</v>
+        <v>90964</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1027,21 +1027,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>353</v>
+        <v>5442</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1051,10 +1051,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>556360</v>
+        <v>556358</v>
       </c>
       <c r="R5" t="n">
-        <v>6510120</v>
+        <v>6510128</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1086,7 +1086,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 31821-2021 artfynd.xlsx
+++ b/artfynd/A 31821-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122651416</v>
+        <v>122651411</v>
       </c>
       <c r="B2" t="n">
-        <v>90909</v>
+        <v>78411</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5447</v>
+        <v>353</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>556434</v>
+        <v>556360</v>
       </c>
       <c r="R2" t="n">
-        <v>6510117</v>
+        <v>6510120</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122651415</v>
+        <v>122651412</v>
       </c>
       <c r="B3" t="n">
-        <v>95126</v>
+        <v>90964</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -799,25 +799,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2180</v>
+        <v>5442</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>556376</v>
+        <v>556358</v>
       </c>
       <c r="R3" t="n">
-        <v>6510108</v>
+        <v>6510128</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122651411</v>
+        <v>122651415</v>
       </c>
       <c r="B4" t="n">
-        <v>78411</v>
+        <v>95126</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -911,25 +911,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>353</v>
+        <v>2180</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -939,10 +939,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>556360</v>
+        <v>556376</v>
       </c>
       <c r="R4" t="n">
-        <v>6510120</v>
+        <v>6510108</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -974,7 +974,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122651412</v>
+        <v>122651416</v>
       </c>
       <c r="B5" t="n">
-        <v>90964</v>
+        <v>90909</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1023,25 +1023,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5442</v>
+        <v>5447</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1051,10 +1051,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>556358</v>
+        <v>556434</v>
       </c>
       <c r="R5" t="n">
-        <v>6510128</v>
+        <v>6510117</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1086,7 +1086,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 31821-2021 artfynd.xlsx
+++ b/artfynd/A 31821-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122651411</v>
+        <v>122651416</v>
       </c>
       <c r="B2" t="n">
-        <v>78411</v>
+        <v>90909</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>353</v>
+        <v>5447</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>556360</v>
+        <v>556434</v>
       </c>
       <c r="R2" t="n">
-        <v>6510120</v>
+        <v>6510117</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -899,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122651415</v>
+        <v>122651411</v>
       </c>
       <c r="B4" t="n">
-        <v>95126</v>
+        <v>78411</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -911,25 +911,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2180</v>
+        <v>353</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -939,10 +939,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>556376</v>
+        <v>556360</v>
       </c>
       <c r="R4" t="n">
-        <v>6510108</v>
+        <v>6510120</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -974,7 +974,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122651416</v>
+        <v>122651415</v>
       </c>
       <c r="B5" t="n">
-        <v>90909</v>
+        <v>95128</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1027,21 +1027,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5447</v>
+        <v>2180</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1051,10 +1051,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>556434</v>
+        <v>556376</v>
       </c>
       <c r="R5" t="n">
-        <v>6510117</v>
+        <v>6510108</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1086,7 +1086,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 31821-2021 artfynd.xlsx
+++ b/artfynd/A 31821-2021 artfynd.xlsx
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122651412</v>
+        <v>122651411</v>
       </c>
       <c r="B3" t="n">
-        <v>90964</v>
+        <v>78411</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,21 +803,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5442</v>
+        <v>353</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>556358</v>
+        <v>556360</v>
       </c>
       <c r="R3" t="n">
-        <v>6510128</v>
+        <v>6510120</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122651411</v>
+        <v>122651412</v>
       </c>
       <c r="B4" t="n">
-        <v>78411</v>
+        <v>90964</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,21 +915,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>353</v>
+        <v>5442</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -939,10 +939,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>556360</v>
+        <v>556358</v>
       </c>
       <c r="R4" t="n">
-        <v>6510120</v>
+        <v>6510128</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -974,7 +974,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 31821-2021 artfynd.xlsx
+++ b/artfynd/A 31821-2021 artfynd.xlsx
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122651411</v>
+        <v>122651412</v>
       </c>
       <c r="B3" t="n">
-        <v>78411</v>
+        <v>90964</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,21 +803,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>353</v>
+        <v>5442</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>556360</v>
+        <v>556358</v>
       </c>
       <c r="R3" t="n">
-        <v>6510120</v>
+        <v>6510128</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122651412</v>
+        <v>122651411</v>
       </c>
       <c r="B4" t="n">
-        <v>90964</v>
+        <v>78411</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,21 +915,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5442</v>
+        <v>353</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -939,10 +939,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>556358</v>
+        <v>556360</v>
       </c>
       <c r="R4" t="n">
-        <v>6510128</v>
+        <v>6510120</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -974,7 +974,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 31821-2021 artfynd.xlsx
+++ b/artfynd/A 31821-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122651416</v>
+        <v>122651412</v>
       </c>
       <c r="B2" t="n">
-        <v>90909</v>
+        <v>90964</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5447</v>
+        <v>5442</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>556434</v>
+        <v>556358</v>
       </c>
       <c r="R2" t="n">
-        <v>6510117</v>
+        <v>6510128</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122651412</v>
+        <v>122651411</v>
       </c>
       <c r="B3" t="n">
-        <v>90964</v>
+        <v>78411</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,21 +803,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5442</v>
+        <v>353</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>556358</v>
+        <v>556360</v>
       </c>
       <c r="R3" t="n">
-        <v>6510128</v>
+        <v>6510120</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122651411</v>
+        <v>122651415</v>
       </c>
       <c r="B4" t="n">
-        <v>78411</v>
+        <v>95128</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -911,25 +911,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>353</v>
+        <v>2180</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -939,10 +939,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>556360</v>
+        <v>556376</v>
       </c>
       <c r="R4" t="n">
-        <v>6510120</v>
+        <v>6510108</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -974,7 +974,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122651415</v>
+        <v>122651416</v>
       </c>
       <c r="B5" t="n">
-        <v>95128</v>
+        <v>90909</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1027,21 +1027,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2180</v>
+        <v>5447</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1051,10 +1051,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>556376</v>
+        <v>556434</v>
       </c>
       <c r="R5" t="n">
-        <v>6510108</v>
+        <v>6510117</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1086,7 +1086,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 31821-2021 artfynd.xlsx
+++ b/artfynd/A 31821-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122651412</v>
+        <v>122651411</v>
       </c>
       <c r="B2" t="n">
-        <v>90964</v>
+        <v>78411</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5442</v>
+        <v>353</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>556358</v>
+        <v>556360</v>
       </c>
       <c r="R2" t="n">
-        <v>6510128</v>
+        <v>6510120</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122651411</v>
+        <v>122651415</v>
       </c>
       <c r="B3" t="n">
-        <v>78411</v>
+        <v>95136</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -799,25 +799,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>353</v>
+        <v>2180</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>556360</v>
+        <v>556376</v>
       </c>
       <c r="R3" t="n">
-        <v>6510120</v>
+        <v>6510108</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122651415</v>
+        <v>122651412</v>
       </c>
       <c r="B4" t="n">
-        <v>95128</v>
+        <v>90972</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -911,25 +911,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2180</v>
+        <v>5442</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -939,10 +939,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>556376</v>
+        <v>556358</v>
       </c>
       <c r="R4" t="n">
-        <v>6510108</v>
+        <v>6510128</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -974,7 +974,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1014,7 +1014,7 @@
         <v>122651416</v>
       </c>
       <c r="B5" t="n">
-        <v>90909</v>
+        <v>90917</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>

--- a/artfynd/A 31821-2021 artfynd.xlsx
+++ b/artfynd/A 31821-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122651411</v>
+        <v>122651412</v>
       </c>
       <c r="B2" t="n">
-        <v>78411</v>
+        <v>90972</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>353</v>
+        <v>5442</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>556360</v>
+        <v>556358</v>
       </c>
       <c r="R2" t="n">
-        <v>6510120</v>
+        <v>6510128</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122651415</v>
+        <v>122651411</v>
       </c>
       <c r="B3" t="n">
-        <v>95136</v>
+        <v>78411</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -799,25 +799,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2180</v>
+        <v>353</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>556376</v>
+        <v>556360</v>
       </c>
       <c r="R3" t="n">
-        <v>6510108</v>
+        <v>6510120</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122651412</v>
+        <v>122651416</v>
       </c>
       <c r="B4" t="n">
-        <v>90972</v>
+        <v>90917</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -911,25 +911,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5442</v>
+        <v>5447</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -939,10 +939,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>556358</v>
+        <v>556434</v>
       </c>
       <c r="R4" t="n">
-        <v>6510128</v>
+        <v>6510117</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -974,7 +974,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122651416</v>
+        <v>122651415</v>
       </c>
       <c r="B5" t="n">
-        <v>90917</v>
+        <v>95136</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1027,21 +1027,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5447</v>
+        <v>2180</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1051,10 +1051,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>556434</v>
+        <v>556376</v>
       </c>
       <c r="R5" t="n">
-        <v>6510117</v>
+        <v>6510108</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1086,7 +1086,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 31821-2021 artfynd.xlsx
+++ b/artfynd/A 31821-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122651412</v>
+        <v>122651411</v>
       </c>
       <c r="B2" t="n">
-        <v>90972</v>
+        <v>78411</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5442</v>
+        <v>353</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>556358</v>
+        <v>556360</v>
       </c>
       <c r="R2" t="n">
-        <v>6510128</v>
+        <v>6510120</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122651411</v>
+        <v>122651412</v>
       </c>
       <c r="B3" t="n">
-        <v>78411</v>
+        <v>90972</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,21 +803,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>353</v>
+        <v>5442</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>556360</v>
+        <v>556358</v>
       </c>
       <c r="R3" t="n">
-        <v>6510120</v>
+        <v>6510128</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 31821-2021 artfynd.xlsx
+++ b/artfynd/A 31821-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122651411</v>
+        <v>122651412</v>
       </c>
       <c r="B2" t="n">
-        <v>78411</v>
+        <v>90972</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>353</v>
+        <v>5442</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>556360</v>
+        <v>556358</v>
       </c>
       <c r="R2" t="n">
-        <v>6510120</v>
+        <v>6510128</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122651412</v>
+        <v>122651411</v>
       </c>
       <c r="B3" t="n">
-        <v>90972</v>
+        <v>78411</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,21 +803,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5442</v>
+        <v>353</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>556358</v>
+        <v>556360</v>
       </c>
       <c r="R3" t="n">
-        <v>6510128</v>
+        <v>6510120</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 31821-2021 artfynd.xlsx
+++ b/artfynd/A 31821-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122651412</v>
+        <v>122651411</v>
       </c>
       <c r="B2" t="n">
-        <v>90972</v>
+        <v>78411</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5442</v>
+        <v>353</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>556358</v>
+        <v>556360</v>
       </c>
       <c r="R2" t="n">
-        <v>6510128</v>
+        <v>6510120</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122651411</v>
+        <v>122651416</v>
       </c>
       <c r="B3" t="n">
-        <v>78411</v>
+        <v>90917</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -799,25 +799,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>353</v>
+        <v>5447</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>556360</v>
+        <v>556434</v>
       </c>
       <c r="R3" t="n">
-        <v>6510120</v>
+        <v>6510117</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122651416</v>
+        <v>122651415</v>
       </c>
       <c r="B4" t="n">
-        <v>90917</v>
+        <v>95136</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,21 +915,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5447</v>
+        <v>2180</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -939,10 +939,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>556434</v>
+        <v>556376</v>
       </c>
       <c r="R4" t="n">
-        <v>6510117</v>
+        <v>6510108</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -974,7 +974,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122651415</v>
+        <v>122651412</v>
       </c>
       <c r="B5" t="n">
-        <v>95136</v>
+        <v>90972</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1023,25 +1023,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2180</v>
+        <v>5442</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1051,10 +1051,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>556376</v>
+        <v>556358</v>
       </c>
       <c r="R5" t="n">
-        <v>6510108</v>
+        <v>6510128</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1086,7 +1086,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 31821-2021 artfynd.xlsx
+++ b/artfynd/A 31821-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,12 +678,7 @@
         <v>122651411</v>
       </c>
       <c r="B2" t="n">
-        <v>78411</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -787,37 +782,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122651416</v>
+        <v>122651413</v>
       </c>
       <c r="B3" t="n">
-        <v>90917</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>90932</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5447</v>
+        <v>1962</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>556434</v>
+        <v>556316</v>
       </c>
       <c r="R3" t="n">
-        <v>6510117</v>
+        <v>6510085</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -862,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -902,12 +892,7 @@
         <v>122651415</v>
       </c>
       <c r="B4" t="n">
-        <v>95136</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96708</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1014,12 +999,7 @@
         <v>122651412</v>
       </c>
       <c r="B5" t="n">
-        <v>90972</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1120,6 +1100,220 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>122651416</v>
+      </c>
+      <c r="B6" t="n">
+        <v>91872</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Simfallet, Ög</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>556434</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6510117</v>
+      </c>
+      <c r="S6" t="n">
+        <v>5</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Finspång</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Risinge</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2024-10-22</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>12:49</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2024-10-22</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>12:49</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Tore Dahlberg</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Tore Dahlberg</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>122651417</v>
+      </c>
+      <c r="B7" t="n">
+        <v>79946</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Simfallet, Ög</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>556486</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6510149</v>
+      </c>
+      <c r="S7" t="n">
+        <v>5</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Finspång</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Risinge</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2024-10-22</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>12:44</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2024-10-22</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>12:44</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Tore Dahlberg</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Tore Dahlberg</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
